--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/exercise-controller/createExercise-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/exercise-controller/createExercise-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="116">
-  <si>
-    <t>Statement: exercise-controller.createExercise(data) – Server Action. Validates CreateExerciseInput via createExerciseSchema (name ≥8 chars ≤64, muscleGroup enum, equipmentNeeded enum). Delegates to exerciseService.createExercise(). Returns ActionResult&lt;Exercise&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="188">
+  <si>
+    <t>Statement: createExercise(data) – Validates the create-exercise input and returns an ActionResult&lt;Exercise&gt;. Returns success with the created Exercise on success. description is optional and may be omitted. Returns a field-level validation error for schema failures without calling the service. name is required, must be 8–64 characters after trimming, and must not be whitespace-only. muscleGroup must be one of the valid MuscleGroup enum values. equipmentNeeded must be one of the valid Equipment enum values. description, when provided, must be at most 1024 characters. Returns a failure with the service error message for ConflictError. Returns a failure with a generic error message for unexpected errors.</t>
   </si>
   <si>
     <t/>
@@ -31,27 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: CreateExerciseInput { name, description?, muscleGroup, equipmentNeeded }</t>
+    <t>Input: data: CreateExerciseInput { name: string, muscleGroup: MuscleGroup, equipmentNeeded: Equipment, description?: string }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>exerciseService.createExercise is mock-injected</t>
+    <t>Valid MuscleGroup values: CHEST, BACK, LEGS, SHOULDERS, ARMS, CORE. Valid Equipment values: BARBELL, DUMBBELL, MACHINE, CABLE. name rules: 8–64 characters after trimming, not whitespace-only. description rules: optional, at most 1024 characters when provided.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;Exercise&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;Exercise&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: Exercise returned.
-On validation failure: errors returned.
-On AppError: message returned.</t>
+    <t>On success: exercise created successfully, returned data matches the created exercise. On validation failure: field-level validation error returned, the service is not called. On service error: operation fails with the service error message. On unexpected error: operation fails with generic error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,193 +64,409 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>all fields valid</t>
-  </si>
-  <si>
-    <t>name ≥ 8 chars, valid enum values</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>All required fields valid, description provided → exercise created successfully, returned data matches the created exercise</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>All required fields valid, description omitted → exercise created successfully, returned data has description undefined</t>
+  </si>
+  <si>
+    <t>name required</t>
+  </si>
+  <si>
+    <t>name omitted → validation fails: name field error returned</t>
+  </si>
+  <si>
+    <t>muscleGroup required</t>
+  </si>
+  <si>
+    <t>muscleGroup omitted → validation fails: muscleGroup field error returned</t>
+  </si>
+  <si>
+    <t>equipmentNeeded required</t>
+  </si>
+  <si>
+    <t>equipmentNeeded omitted → validation fails: equipmentNeeded field error returned</t>
+  </si>
+  <si>
+    <t>name value</t>
+  </si>
+  <si>
+    <t>name is empty string → validation fails: name field error returned</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>Exercise name is already in use (ConflictError "Name already in use") → operation fails with message "Name already in use"</t>
+  </si>
+  <si>
+    <t>Unexpected error</t>
+  </si>
+  <si>
+    <t>An unexpected error occurs → operation fails with generic error message "An unexpected error occurred"</t>
+  </si>
+  <si>
+    <t>No TC</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Input Data</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>all required fields provided with valid values, exercise is created successfully</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data matches the created exercise</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>name: "Standard Bench Press", muscleGroup: CHEST, equipmentNeeded: BARBELL, description omitted</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data has description undefined</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>all required fields provided with valid values, name field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: name field error returned</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>all required fields provided with valid values, muscleGroup field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: muscleGroup field error returned</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>all required fields provided with valid values, equipmentNeeded field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: equipmentNeeded field error returned</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>all required fields provided with valid values, name set to "" (empty string)</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>all required fields provided with valid values, exercise name is already in use (ConflictError)</t>
+  </si>
+  <si>
+    <t>operation fails with message "Name already in use"</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>all required fields provided with valid values, an unexpected error occurs</t>
+  </si>
+  <si>
+    <t>operation fails with generic error message "An unexpected error occurred"</t>
+  </si>
+  <si>
+    <t>Number BVA</t>
+  </si>
+  <si>
+    <t>BVA Test Case</t>
+  </si>
+  <si>
+    <t>name whitespace</t>
+  </si>
+  <si>
+    <t>name: whitespace-only string → validation fails: name field error returned</t>
+  </si>
+  <si>
+    <t>name: "   Bench Press   " (valid content padded with whitespace) → trimmed and accepted, exercise created successfully</t>
   </si>
   <si>
     <t>name length</t>
   </si>
   <si>
-    <t>name ≥ 8 chars</t>
-  </si>
-  <si>
-    <t>name &lt; 8 chars → validation error</t>
+    <t>name: 7 chars (min - 1): below minimum → validation fails: name field error returned</t>
+  </si>
+  <si>
+    <t>name: 8 chars (min): at minimum → exercise created successfully</t>
+  </si>
+  <si>
+    <t>name: 9 chars (min + 1): above minimum → exercise created successfully</t>
+  </si>
+  <si>
+    <t>name: 63 chars (max - 1): below maximum → exercise created successfully</t>
+  </si>
+  <si>
+    <t>name: 64 chars (max): at maximum → exercise created successfully</t>
+  </si>
+  <si>
+    <t>name: 65 chars (max + 1): above maximum → validation fails: name field error returned</t>
+  </si>
+  <si>
+    <t>description length</t>
+  </si>
+  <si>
+    <t>description: 1023 chars (max - 1): below maximum → exercise created successfully</t>
+  </si>
+  <si>
+    <t>description: 1024 chars (max): at maximum → exercise created successfully</t>
+  </si>
+  <si>
+    <t>description: 1025 chars (max + 1): above maximum → validation fails: description field error returned</t>
   </si>
   <si>
     <t>muscleGroup enum</t>
   </si>
   <si>
-    <t>valid MuscleGroup value</t>
-  </si>
-  <si>
-    <t>invalid MuscleGroup → validation error</t>
-  </si>
-  <si>
-    <t>equipment enum</t>
-  </si>
-  <si>
-    <t>valid Equipment value</t>
-  </si>
-  <si>
-    <t>invalid Equipment → validation error</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves Exercise</t>
-  </si>
-  <si>
-    <t>throws ConflictError → failure with message</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
-  </si>
-  <si>
-    <t>No TC</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>Input Data</t>
-  </si>
-  <si>
-    <t>Expected</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>1,2,4,6,8</t>
-  </si>
-  <si>
-    <t>VALID_EXERCISE_INPUT, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true, data: Exercise }</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ name: "Ab", muscleGroup: "CHEST", equipment: "BARBELL" }</t>
-  </si>
-  <si>
-    <t>{ success: false, errors defined }</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>{ name: "Bench Press", muscleGroup: "INVALID_GROUP" }</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>{ name: "Bench Press", equipmentNeeded: "INVALID" }</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>valid input, service throws ConflictError</t>
-  </si>
-  <si>
-    <t>{ success: false, message from error }</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>valid input, service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
-  </si>
-  <si>
-    <t>Number BVA</t>
-  </si>
-  <si>
-    <t>BVA Test Case</t>
-  </si>
-  <si>
-    <t>name length boundary</t>
-  </si>
-  <si>
-    <t>name 7 chars → invalid (below min)</t>
-  </si>
-  <si>
-    <t>name 8 chars → valid (at min)</t>
-  </si>
-  <si>
-    <t>name 64 chars → valid (at max)</t>
-  </si>
-  <si>
-    <t>name 65 chars → invalid (above max)</t>
-  </si>
-  <si>
-    <t>name length interior</t>
-  </si>
-  <si>
-    <t>name 9 chars → valid (min+1)</t>
-  </si>
-  <si>
-    <t>name 63 chars → valid (max-1)</t>
+    <t>muscleGroup: CHEST (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>muscleGroup: BACK (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>muscleGroup: LEGS (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>muscleGroup: SHOULDERS (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>muscleGroup: ARMS (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>muscleGroup: CORE (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>muscleGroup: "INVALID" (not a valid enum value) → validation fails: muscleGroup field error returned</t>
+  </si>
+  <si>
+    <t>equipmentNeeded enum</t>
+  </si>
+  <si>
+    <t>equipmentNeeded: BARBELL (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>equipmentNeeded: DUMBBELL (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>equipmentNeeded: MACHINE (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>equipmentNeeded: CABLE (valid enum value) → exercise created successfully</t>
+  </si>
+  <si>
+    <t>equipmentNeeded: "INVALID" (not a valid enum value) → validation fails: equipmentNeeded field error returned</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>name=7 chars</t>
-  </si>
-  <si>
-    <t>{ name: "1234567" }</t>
-  </si>
-  <si>
-    <t>success=false, errors.name defined</t>
-  </si>
-  <si>
-    <t>name=8 chars</t>
-  </si>
-  <si>
-    <t>{ name: "12345678" }</t>
-  </si>
-  <si>
-    <t>schema passes (min boundary)</t>
-  </si>
-  <si>
-    <t>name=64 chars</t>
-  </si>
-  <si>
-    <t>{ name: "a".repeat(64) }</t>
-  </si>
-  <si>
-    <t>schema passes (max boundary)</t>
-  </si>
-  <si>
-    <t>name=65 chars</t>
-  </si>
-  <si>
-    <t>{ name: "a".repeat(65) }</t>
-  </si>
-  <si>
-    <t>name=9 chars</t>
-  </si>
-  <si>
-    <t>{ name: "BenchPrs1" }</t>
-  </si>
-  <si>
-    <t>success=true</t>
-  </si>
-  <si>
-    <t>name=63 chars</t>
-  </si>
-  <si>
-    <t>{ name: "b".repeat(63) }</t>
+    <t>BVA-1  (name=ws)</t>
+  </si>
+  <si>
+    <t>all required fields valid, name: "         " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>BVA-2  (name=padded)</t>
+  </si>
+  <si>
+    <t>all required fields valid, name: "   Bench Press   " (padded with whitespace)</t>
+  </si>
+  <si>
+    <t>BVA-3  (name=7)</t>
+  </si>
+  <si>
+    <t>all required fields valid, name: "A".repeat(7)</t>
+  </si>
+  <si>
+    <t>BVA-4  (name=8)</t>
+  </si>
+  <si>
+    <t>all required fields valid, name: "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data name matches the input</t>
+  </si>
+  <si>
+    <t>BVA-5  (name=9)</t>
+  </si>
+  <si>
+    <t>all required fields valid, name: "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>BVA-6  (name=63)</t>
+  </si>
+  <si>
+    <t>all required fields valid, name: "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>BVA-7  (name=64)</t>
+  </si>
+  <si>
+    <t>all required fields valid, name: "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>BVA-8  (name=65)</t>
+  </si>
+  <si>
+    <t>all required fields valid, name: "A".repeat(65)</t>
+  </si>
+  <si>
+    <t>BVA-9  (desc=1023)</t>
+  </si>
+  <si>
+    <t>all required fields valid, description: "A".repeat(1023)</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data description matches the input</t>
+  </si>
+  <si>
+    <t>BVA-10 (desc=1024)</t>
+  </si>
+  <si>
+    <t>all required fields valid, description: "A".repeat(1024)</t>
+  </si>
+  <si>
+    <t>BVA-11 (desc=1025)</t>
+  </si>
+  <si>
+    <t>all required fields valid, description: "A".repeat(1025)</t>
+  </si>
+  <si>
+    <t>validation fails: description field error returned</t>
+  </si>
+  <si>
+    <t>BVA-12 (mg=CHEST)</t>
+  </si>
+  <si>
+    <t>all required fields valid, muscleGroup: CHEST</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data muscleGroup is CHEST</t>
+  </si>
+  <si>
+    <t>BVA-13 (mg=BACK)</t>
+  </si>
+  <si>
+    <t>all required fields valid, muscleGroup: BACK</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data muscleGroup is BACK</t>
+  </si>
+  <si>
+    <t>BVA-14 (mg=LEGS)</t>
+  </si>
+  <si>
+    <t>all required fields valid, muscleGroup: LEGS</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data muscleGroup is LEGS</t>
+  </si>
+  <si>
+    <t>BVA-15 (mg=SHOULDERS)</t>
+  </si>
+  <si>
+    <t>all required fields valid, muscleGroup: SHOULDERS</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data muscleGroup is SHOULDERS</t>
+  </si>
+  <si>
+    <t>BVA-16 (mg=ARMS)</t>
+  </si>
+  <si>
+    <t>all required fields valid, muscleGroup: ARMS</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data muscleGroup is ARMS</t>
+  </si>
+  <si>
+    <t>BVA-17 (mg=CORE)</t>
+  </si>
+  <si>
+    <t>all required fields valid, muscleGroup: CORE</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data muscleGroup is CORE</t>
+  </si>
+  <si>
+    <t>BVA-18 (mg=INVALID)</t>
+  </si>
+  <si>
+    <t>all required fields valid, muscleGroup: "INVALID" (not a valid enum value)</t>
+  </si>
+  <si>
+    <t>BVA-19 (eq=BARBELL)</t>
+  </si>
+  <si>
+    <t>all required fields valid, equipmentNeeded: BARBELL</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data equipmentNeeded is BARBELL</t>
+  </si>
+  <si>
+    <t>BVA-20 (eq=DUMBBELL)</t>
+  </si>
+  <si>
+    <t>all required fields valid, equipmentNeeded: DUMBBELL</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data equipmentNeeded is DUMBBELL</t>
+  </si>
+  <si>
+    <t>BVA-21 (eq=MACHINE)</t>
+  </si>
+  <si>
+    <t>all required fields valid, equipmentNeeded: MACHINE</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data equipmentNeeded is MACHINE</t>
+  </si>
+  <si>
+    <t>BVA-22 (eq=CABLE)</t>
+  </si>
+  <si>
+    <t>all required fields valid, equipmentNeeded: CABLE</t>
+  </si>
+  <si>
+    <t>exercise created successfully, returned data equipmentNeeded is CABLE</t>
+  </si>
+  <si>
+    <t>BVA-23 (eq=INVALID)</t>
+  </si>
+  <si>
+    <t>all required fields valid, equipmentNeeded: "INVALID" (not a valid enum value)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -261,70 +475,73 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
+    <t>BVA-1</t>
   </si>
   <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>Valid input (name ≥ 8), service resolves</t>
-  </si>
-  <si>
-    <t>success=true, Exercise returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>Name "Ab" (2 chars)</t>
-  </si>
-  <si>
-    <t>success=false, errors defined</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Invalid muscleGroup</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Invalid equipment</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Service throws ConflictError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-6</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
   </si>
   <si>
     <t>BVA-5</t>
   </si>
   <si>
-    <t>Name 9 chars</t>
-  </si>
-  <si>
     <t>BVA-6</t>
   </si>
   <si>
-    <t>Name 63 chars</t>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
+  </si>
+  <si>
+    <t>BVA-18</t>
+  </si>
+  <si>
+    <t>BVA-19</t>
+  </si>
+  <si>
+    <t>BVA-20</t>
+  </si>
+  <si>
+    <t>BVA-21</t>
+  </si>
+  <si>
+    <t>BVA-22</t>
+  </si>
+  <si>
+    <t>BVA-23</t>
   </si>
   <si>
     <t>Testing</t>
@@ -357,16 +574,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-01</t>
+    <t>CTRL-15</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -882,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -937,13 +1151,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -951,13 +1165,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -965,13 +1179,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -979,13 +1193,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -993,13 +1207,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1007,41 +1221,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1052,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1064,19 +1250,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1084,16 +1270,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1101,16 +1287,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1118,16 +1304,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1135,16 +1321,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1152,16 +1338,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1169,16 +1355,50 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1189,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1199,13 +1419,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1213,65 +1433,252 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1282,7 +1689,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1294,19 +1701,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1314,16 +1721,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1331,16 +1738,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1348,16 +1755,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1365,16 +1772,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1382,16 +1789,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1399,16 +1806,305 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>75</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1419,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1432,22 +2128,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1455,19 +2151,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1475,19 +2171,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1495,19 +2191,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1515,19 +2211,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1535,19 +2231,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1555,19 +2251,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1575,19 +2271,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1595,19 +2291,479 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>75</v>
+      <c r="E14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1635,16 +2791,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1652,45 +2808,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>112</v>
+      <c r="A3" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="B3" s="1">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1699,19 +2855,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>113</v>
+        <v>186</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>115</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
